--- a/main/ig/StructureDefinition-EyeColor.xlsx
+++ b/main/ig/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T15:01:44+00:00</t>
+    <t>2025-12-29T16:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EyeColor.xlsx
+++ b/main/ig/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T16:38:49+00:00</t>
+    <t>2026-01-16T16:18:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EyeColor.xlsx
+++ b/main/ig/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-16T16:18:56+00:00</t>
+    <t>2026-01-23T13:13:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EyeColor.xlsx
+++ b/main/ig/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T13:13:49+00:00</t>
+    <t>2026-01-23T13:18:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EyeColor.xlsx
+++ b/main/ig/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T13:18:01+00:00</t>
+    <t>2026-04-22T13:48:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-EyeColor.xlsx
+++ b/main/ig/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T13:48:02+00:00</t>
+    <t>2026-05-07T08:58:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EyeColor.xlsx
+++ b/main/ig/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T08:58:39+00:00</t>
+    <t>2026-05-29T12:14:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EyeColor.xlsx
+++ b/main/ig/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-29T12:14:59+00:00</t>
+    <t>2026-05-29T12:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EyeColor.xlsx
+++ b/main/ig/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-29T12:18:04+00:00</t>
+    <t>2026-05-29T12:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
